--- a/reviews/REVIEWED_StateRepHong_20210107_20210628_20260806_autoPush.xlsx
+++ b/reviews/REVIEWED_StateRepHong_20210107_20210628_20260806_autoPush.xlsx
@@ -7335,7 +7335,7 @@
         <v>0</v>
       </c>
       <c r="J159" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K159" t="inlineStr"/>
     </row>
